--- a/output/pdf_financials_xlsx/LFG.xlsx
+++ b/output/pdf_financials_xlsx/LFG.xlsx
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.115162</v>
       </c>
     </row>
     <row r="92">
@@ -2050,13 +2050,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.599222</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.303292</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.672077</v>
       </c>
     </row>
     <row r="93">
@@ -3430,7 +3430,11 @@
           <t>Reserve (Note 13)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -3459,7 +3463,11 @@
           <t>Translation reserve</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -4006,7 +4014,11 @@
           <t>Reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>0.599222</v>
       </c>

--- a/output/pdf_financials_xlsx/LFG.xlsx
+++ b/output/pdf_financials_xlsx/LFG.xlsx
@@ -1096,13 +1096,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.009218</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.415562</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.300777</v>
       </c>
     </row>
     <row r="35">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.009218</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.415562</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.300777</v>
       </c>
     </row>
     <row r="37">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.012689</v>
+        <v>0.003471</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.419033</v>
+        <v>0.003471</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">

--- a/output/pdf_financials_xlsx/LFG.xlsx
+++ b/output/pdf_financials_xlsx/LFG.xlsx
@@ -490,10 +490,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D4" s="3" t="n">
+        <v>0.267233</v>
       </c>
     </row>
     <row r="5">
@@ -510,10 +508,8 @@
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D5" s="3" t="n">
+        <v>0.015688</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +528,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D6" s="3" t="n">
+        <v>0.251545</v>
       </c>
     </row>
     <row r="7">
@@ -550,12 +544,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.270121</v>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.206866</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.178979</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +564,8 @@
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -592,10 +582,8 @@
       <c r="C9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -610,12 +598,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.270121</v>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.918088</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>20.580912</v>
       </c>
     </row>
     <row r="11">
@@ -634,10 +620,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D11" s="3" t="n">
+        <v>-20.329367</v>
       </c>
     </row>
     <row r="12">
@@ -654,10 +638,8 @@
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -674,10 +656,8 @@
       <c r="C13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -694,10 +674,8 @@
       <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -714,10 +692,8 @@
       <c r="C15" s="3" t="n">
         <v>0.006582</v>
       </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -731,15 +707,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C16" s="3" t="n">
+        <v>-1.918088</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-20.13164</v>
       </c>
     </row>
     <row r="17">
@@ -756,10 +728,8 @@
       <c r="C17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -817,15 +787,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C20" s="3" t="n">
+        <v>-1.918088</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-20.13164</v>
       </c>
     </row>
     <row r="21">
@@ -842,10 +808,8 @@
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -862,10 +826,8 @@
       <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -879,15 +841,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C23" s="3" t="n">
+        <v>-1.918088</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-20.13164</v>
       </c>
     </row>
     <row r="24">
@@ -902,12 +860,10 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.25</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="25">
@@ -922,12 +878,10 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.25</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="26">
@@ -941,15 +895,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C26" s="3" t="n">
+        <v>7.672352</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>59.210706</v>
       </c>
     </row>
     <row r="27">
@@ -963,15 +913,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C27" s="3" t="n">
+        <v>-1.918088</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-20.13164</v>
       </c>
     </row>
     <row r="28">
@@ -988,10 +934,8 @@
       <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1005,15 +949,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C29" s="3" t="n">
+        <v>-1.918088</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-20.13164</v>
       </c>
     </row>
     <row r="30">
@@ -1032,10 +972,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D30" s="3" t="n">
+        <v>-7533.36601392792</v>
       </c>
     </row>
     <row r="31">
@@ -1049,15 +987,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1076,10 +1010,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D32" s="3" t="n">
+        <v>-7533.36601392792</v>
       </c>
     </row>
     <row r="33">
@@ -1634,13 +1566,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.728064</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.644766</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.303505</v>
       </c>
     </row>
     <row r="68">
@@ -2157,15 +2089,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C99" s="3" t="n">
+        <v>-1.918088</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-20.13164</v>
       </c>
     </row>
     <row r="100">
@@ -2182,10 +2110,8 @@
       <c r="C100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2200,12 +2126,10 @@
         </is>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.001123</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0.143312</v>
       </c>
     </row>
     <row r="102">
@@ -2222,10 +2146,8 @@
       <c r="C102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2242,10 +2164,8 @@
       <c r="C103" s="3" t="n">
         <v>0.008319</v>
       </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D103" s="3" t="n">
+        <v>-0.198194</v>
       </c>
     </row>
     <row r="104">
@@ -2260,12 +2180,10 @@
         </is>
       </c>
       <c r="C104" s="3" t="n">
-        <v>1.070842</v>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.351612</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0.059771</v>
       </c>
     </row>
     <row r="105">
@@ -2282,10 +2200,8 @@
       <c r="C105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2300,12 +2216,10 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>1.079161</v>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.358808</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0.004889</v>
       </c>
     </row>
     <row r="107">
@@ -2320,12 +2234,10 @@
         </is>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0.446865</v>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.021989</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0.9727170000000001</v>
       </c>
     </row>
     <row r="108">
@@ -2342,10 +2254,8 @@
       <c r="C108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2362,10 +2272,8 @@
       <c r="C109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2382,10 +2290,8 @@
       <c r="C110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2402,10 +2308,8 @@
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2422,10 +2326,8 @@
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2442,10 +2344,8 @@
       <c r="C113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2462,10 +2362,8 @@
       <c r="C114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D114" s="3" t="n">
+        <v>-1.510431</v>
       </c>
     </row>
     <row r="115">
@@ -2482,10 +2380,8 @@
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2502,10 +2398,8 @@
       <c r="C116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2522,10 +2416,8 @@
       <c r="C117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2542,10 +2434,8 @@
       <c r="C118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2560,12 +2450,10 @@
         </is>
       </c>
       <c r="C119" s="3" t="n">
-        <v>-0.491628</v>
-      </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.27799</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>-1.398264</v>
       </c>
     </row>
     <row r="120">
@@ -2582,10 +2470,8 @@
       <c r="C120" s="3" t="n">
         <v>0.006</v>
       </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2602,10 +2488,8 @@
       <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2622,10 +2506,8 @@
       <c r="C122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2642,10 +2524,8 @@
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2662,10 +2542,8 @@
       <c r="C124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2682,10 +2560,8 @@
       <c r="C125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2702,10 +2578,8 @@
       <c r="C126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2742,12 +2616,10 @@
         </is>
       </c>
       <c r="C128" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.019371</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2762,12 +2634,10 @@
         </is>
       </c>
       <c r="C129" s="3" t="n">
-        <v>0.6445</v>
-      </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.523848</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>3.590087</v>
       </c>
     </row>
     <row r="130">
@@ -2782,12 +2652,10 @@
         </is>
       </c>
       <c r="C130" s="3" t="n">
-        <v>0.113346</v>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.009218</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0.415562</v>
       </c>
     </row>
     <row r="131">
@@ -2804,10 +2672,8 @@
       <c r="C131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2822,12 +2688,10 @@
         </is>
       </c>
       <c r="C132" s="3" t="n">
-        <v>-0.104128</v>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.406344</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>-0.114785</v>
       </c>
     </row>
     <row r="133">
@@ -2842,12 +2706,10 @@
         </is>
       </c>
       <c r="C133" s="3" t="n">
-        <v>0.009218</v>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.415562</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0.300777</v>
       </c>
     </row>
     <row r="134">
@@ -2864,10 +2726,8 @@
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2882,12 +2742,10 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.257</v>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.395494</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-2.306608</v>
       </c>
     </row>
   </sheetData>
@@ -2901,7 +2759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4136,25 +3994,31 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>(Restated Note 15) January 31,</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.918088</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-20.13164</v>
       </c>
     </row>
     <row r="40">
@@ -4165,27 +4029,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Net loss $ (1,918,088) $</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-4.213054</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.021989</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.9727170000000001</v>
       </c>
     </row>
     <row r="41">
@@ -4201,21 +4067,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Stock-based compensation 21,989</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Impairment of exploration and evaluation asset</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.446865</v>
+        <v>0.944626</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -4236,7 +4098,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Impairment of mineral properties 944,626</t>
+          <t>Accrued interest on loans payable</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -4246,12 +4108,10 @@
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>3.034927</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.009219</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.202739</v>
       </c>
     </row>
     <row r="43">
@@ -4267,22 +4127,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Accrued interest on loans payable 9,219</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Amortisation</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F43" s="5" t="n">
-        <v>0.005959</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.268143</v>
       </c>
     </row>
     <row r="44">
@@ -4298,7 +4162,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Loss on settlement of debt 300,000</t>
+          <t>Realised loss on digital currencies</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -4312,10 +4176,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G44" s="5" t="n">
+        <v>0.278089</v>
       </c>
     </row>
     <row r="45">
@@ -4326,12 +4188,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GST receivable (1,123)</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -4340,13 +4202,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F45" s="5" t="n">
-        <v>0.021271</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.001318</v>
       </c>
     </row>
     <row r="46">
@@ -4357,31 +4219,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Prepaid expenses -</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
+          <t>Loss on associate</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F46" s="5" t="n">
-        <v>0.008319</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.002441</v>
       </c>
     </row>
     <row r="47">
@@ -4392,31 +4250,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 247,883</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Loss on investments</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F47" s="5" t="n">
-        <v>0.438713</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.348633</v>
       </c>
     </row>
     <row r="48">
@@ -4427,12 +4281,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Net cash flows used in operating activities (395,494)</t>
+          <t>Gain on disposal of subsidiary</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4441,13 +4295,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F48" s="5" t="n">
-        <v>-0.257</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.54636</v>
       </c>
     </row>
     <row r="49">
@@ -4458,12 +4312,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITES</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mineral property acquisition and exploration costs (11,606)</t>
+          <t>Loss on debt settlements</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4473,12 +4327,10 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>-0.491628</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.316154</v>
       </c>
     </row>
     <row r="50">
@@ -4489,17 +4341,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Recovery of exploration and evaluation assets 252,226</t>
+          <t>GST receivable</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4507,15 +4359,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F50" s="5" t="n">
+        <v>-0.001123</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.076351</v>
       </c>
     </row>
     <row r="51">
@@ -4526,15 +4374,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Deposits 37,370</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -4545,10 +4397,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G51" s="5" t="n">
+        <v>0.219663</v>
       </c>
     </row>
     <row r="52">
@@ -4559,17 +4409,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Net cash flows provided by (used in) investing activities 277,990</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4577,13 +4427,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F52" s="5" t="n">
-        <v>-0.491628</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-0.198194</v>
       </c>
     </row>
     <row r="53">
@@ -4594,31 +4444,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of common shares 600,000</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F53" s="5" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-0.009792</v>
       </c>
     </row>
     <row r="54">
@@ -4629,27 +4475,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Share issuance costs (19,371)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>-0.0065</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.247883</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.059771</v>
       </c>
     </row>
     <row r="55">
@@ -4660,31 +4508,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Proceeds from exercise of stock options -</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>IssuanceOfCapitalStock</t>
-        </is>
-      </c>
+          <t>Net change in digital currencies held for working capital</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F55" s="5" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>-0.071506</v>
       </c>
     </row>
     <row r="56">
@@ -4695,27 +4539,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Proceeds from (repayment of) promissory note (56,781)</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Net cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.395494</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>-2.306608</v>
       </c>
     </row>
     <row r="57">
@@ -4726,26 +4572,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Net cash flows provided by financing activities 523,848</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Mineral property acquisition and exploration costs</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.6445</v>
+        <v>-0.011606</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -4761,31 +4603,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Net increase (decrease) in cash 406,344</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Cash recovery on disposal of subsidiary</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F58" s="5" t="n">
-        <v>-0.104128</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.000283</v>
       </c>
     </row>
     <row r="59">
@@ -4796,31 +4634,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cash, beginning of year 9,218</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Fees paid for partnership agreement</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F59" s="5" t="n">
-        <v>0.113346</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="60">
@@ -4831,26 +4665,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cash, end of year $ 415,562 $</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Recovery of E&amp;E costs</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.009218</v>
+        <v>0.252226</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -4866,26 +4696,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Non-cash activity</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures included within accounts payable $ 620,523</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0.6321290000000001</v>
+        <v>0.03737</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4901,17 +4727,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Non-cash activity</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Shares issued for settlement of accounts payable $ 483,206 $</t>
+          <t>Purchase of investments</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>PurchaseOfInvestment</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4924,10 +4750,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G62" s="5" t="n">
+        <v>-1.510431</v>
       </c>
     </row>
     <row r="63">
@@ -4938,12 +4762,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Non-cash activity</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Shares issued for settlement of loans payable $ 116,794 $</t>
+          <t>Proceeds from sale of digital currencies</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -4957,10 +4781,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G63" s="5" t="n">
+        <v>0.411884</v>
       </c>
     </row>
     <row r="64">
@@ -4971,27 +4793,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Non-cash activity</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fair value of shares issued for exploration and evaluation asset $ - $</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Net cash flows provided by (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.38531</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.27799</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>-1.398264</v>
       </c>
     </row>
     <row r="65">
@@ -5002,12 +4826,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Non-cash activity</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fair value of shares issued for promissory note settlement $ - $</t>
+          <t>Proceeds from issuance of equity instruments</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5017,12 +4841,10 @@
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.6</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>3.180574</v>
       </c>
     </row>
     <row r="66">
@@ -5033,12 +4855,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Non-cash activity</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Total 2,891,145 385,310 395,000 (6,500) 150,000 - 6,000 446,865 - (4,213,054) 54,766 127,272 182,038 600,000 (19,371) 600,000 - 21,989 - (1,918,088)</t>
+          <t>Proceeds from issuance of convertible debt, net of legal fees</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -5047,13 +4869,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F66" s="5" t="n">
-        <v>-0.533432</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.409513</v>
       </c>
     </row>
     <row r="67">
@@ -5064,22 +4886,26 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Non-cash activity</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Reserve 288,655 - - - - (60,000) (4,550) 446,865 (71,748) - 599,222 - 599,222 - - - (182,000) 21,989 (135,919) -</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.303292</v>
+        <v>-0.019371</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -5095,12 +4921,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>$             $    $         $                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              statements.</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>$             $    $         $                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              statements. to - - - - - - - - - - - - - - - - - - financial shares 127,272 127,272</t>
+          <t>Repayment of promissory note</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5110,7 +4936,7 @@
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.127272</v>
+        <v>-0.056781</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -5126,27 +4952,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>$                                                     Obligation issue</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>$                                                     Obligation issue $             $    $ these Amount 4,967,271 385,310 395,000 (6,500) 150,000 60,000 10,550 5,961,631 5,961,631 600,000 (19,371) 600,000 182,000</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Net cash flows provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>7.32426</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.523848</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>3.590087</v>
       </c>
     </row>
     <row r="70">
@@ -5157,81 +4985,83 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>equity</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>equity total</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>Net increase (decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F70" s="5" t="n">
+        <v>0.406344</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>-0.114785</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>31, 2025          Ended January</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>(Restated Note 15) 31,</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.009218</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.415562</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Consulting fees $ 13,866 $</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5240,63 +5070,57 @@
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.072121</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.415562</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.300777</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Non-cash activity</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Foreign exchange loss 36,723</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Shares issued for investment in associate</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F73" s="5" t="n">
-        <v>0.006582</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>2.736</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Non-cash activity</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>General and administrative costs (Note 10) 183,096</t>
+          <t>Shares issued for investment in subsidiary</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5305,34 +5129,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F74" s="5" t="n">
-        <v>0.258032</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>13.67685</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Non-cash activity</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Interest expense (Note 7) 10,078</t>
+          <t>Exploration and evaluation expenditures included within accounts payable</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5341,7 +5165,7 @@
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>0.005961</v>
+        <v>0.620523</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -5352,52 +5176,48 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Non-cash activity</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Management fees (Note 10) 193,000</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Fair value of shares issued for digital currencies</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F76" s="5" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>1.575352</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Non-cash activity</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Marketing fees 29,899</t>
+          <t>Shares issued for debt settlement</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -5407,33 +5227,31 @@
         </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>0.008392999999999999</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.116794</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.1837</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Non-cash activity</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Professional fees 158,857</t>
+          <t>Shares issued for settlement of accounts payable</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5442,7 +5260,7 @@
         </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.160431</v>
+        <v>0.483206</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -5453,17 +5271,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Non-cash activity</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Stock-based compensation (Notes 9 and 10) 21,989</t>
+          <t>Total 182,038 600,000 (19,371) 600,000 - 21,989 - (1,918,088) (533,432) (533,432) 3,264,074 - 100,200 2,736,000 13,676,850 1,575,352 1,510,662 115,162 - -</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -5473,28 +5291,26 @@
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>0.446865</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.313228</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>-20.13164</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Non-cash activity</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Transfer agent, regulatory and listing fees 25,954</t>
+          <t>(6,506,087) - - - - 135,919 (1,918,088) (8,288,256) (8,288,256) - - - - - - - - 255,936 19,750 deficit</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -5504,28 +5320,26 @@
         </is>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0.021742</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-28.14421</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>-20.13164</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>$         $  $                                                               Accumulated</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Impairment of mineral properties (Note 5) 944,626</t>
+          <t>$         $  $                                                               Accumulated                              $</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -5534,8 +5348,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F81" s="5" t="n">
-        <v>3.034927</v>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5546,17 +5362,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>115,162                            115,162                                                  reserve                                                                    Translation</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Loss on settlement of debt (Notes 7, 8 and 15) 300,000</t>
+          <t>599,222 - - -  (182,000) 21,989  (135,919) -   303,292              303,292   120,655  (984,500)  (2,346) - - -  1,510,662 -  (255,936)  (19,750) -   672,077                                                                           statements.                                               Reserve $         $  $              $ to - - - - - - - - - - - - - - - - - - financial shares 127,272 127,272</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -5565,31 +5381,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F82" s="5" t="n">
+        <v>0.127272</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.127272</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>and and</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LOSS AND COMPREHENSIVE LOSS $ (1,918,088) $</t>
+          <t>and and</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -5599,42 +5411,32 @@
         </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>-4.213054</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.3e-05</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>1.3e-05</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share (Note 15) $ (0.25) $</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>(Restated Note 15) January 31,</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>-7.4e-07</v>
+        <v>0.002024</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5645,33 +5447,2369 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Net loss $ (1,918,088) $</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>-4.213054</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Non-cash items</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 21,989</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0.446865</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Non-cash items</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Impairment of mineral properties 944,626</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>3.034927</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Non-cash items</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Accrued interest on loans payable 9,219</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>0.005959</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Non-cash items</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Loss on settlement of debt 300,000</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Net changes in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>GST receivable (1,123)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>0.021271</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Net changes in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Prepaid expenses -</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>0.008319</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Net changes in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Accounts payable and accrued liabilities 247,883</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>0.438713</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Net changes in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Net cash flows used in operating activities (395,494)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>-0.257</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>INVESTING ACTIVITES</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Mineral property acquisition and exploration costs (11,606)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>-0.491628</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>INVESTING ACTIVITES</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Recovery of exploration and evaluation assets 252,226</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>INVESTING ACTIVITES</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Deposits 37,370</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>INVESTING ACTIVITES</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Net cash flows provided by (used in) investing activities 277,990</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>-0.491628</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Proceeds from issuance of common shares 600,000</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Share issuance costs (19,371)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Proceeds from exercise of stock options -</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Proceeds from (repayment of) promissory note (56,781)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Net cash flows provided by financing activities 523,848</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>0.6445</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Net increase (decrease) in cash 406,344</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>-0.104128</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Cash, beginning of year 9,218</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>0.113346</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Cash, end of year $ 415,562 $</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>0.009218</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Non-cash activity</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Exploration and evaluation expenditures included within accounts payable $ 620,523</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>0.6321290000000001</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Non-cash activity</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Shares issued for settlement of accounts payable $ 483,206 $</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Non-cash activity</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Shares issued for settlement of loans payable $ 116,794 $</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Non-cash activity</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Fair value of shares issued for exploration and evaluation asset $ - $</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Non-cash activity</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Fair value of shares issued for promissory note settlement $ - $</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Non-cash activity</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Total 2,891,145 385,310 395,000 (6,500) 150,000 - 6,000 446,865 - (4,213,054) 54,766 127,272 182,038 600,000 (19,371) 600,000 - 21,989 - (1,918,088)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>-0.533432</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Non-cash activity</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Reserve 288,655 - - - - (60,000) (4,550) 446,865 (71,748) - 599,222 - 599,222 - - - (182,000) 21,989 (135,919) -</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>0.303292</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>$             $    $         $                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              statements.</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>$             $    $         $                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              statements. to - - - - - - - - - - - - - - - - - - financial shares 127,272 127,272</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>0.127272</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>$                                                     Obligation issue</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>$                                                     Obligation issue $             $    $ these Amount 4,967,271 385,310 395,000 (6,500) 150,000 60,000 10,550 5,961,631 5,961,631 600,000 (19,371) 600,000 182,000</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>7.32426</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>equity</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>equity total</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>INCOME</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Revenue (Note 10) $</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.267233</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>COST OF SALES</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>0.015688</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>COST OF SALES</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>GROSS MARGIN</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0.251545</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>0.013866</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>0.129025</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Exchange loss</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>0.036723</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0.028263</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>General and administrative costs (Note 15)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>0.183096</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>0.474377</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Interest expense (Note 9)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>0.010078</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>0.210126</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Management fees (Note 15)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>0.049954</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Marketing fees</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>0.029899</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>0.747617</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Professional fees (Note 15)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>0.158857</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>0.893958</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Stock-based compensation (Notes 13 and 15)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>0.021989</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0.9727170000000001</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Transfer agent, regulatory and listing fees</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>0.025954</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>0.093066</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Impairment of exploration and evaluation asset</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>0.944626</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Amortisation (Notes 5 and 6)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>0.268143</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Litigation settlement expense</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0.059415</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Realised loss on digital currencies (Note 4)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>0.278089</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Loss on debt settlement (Note 9 and 12)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>0.316154</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Loss on associate (Note 6)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>0.002441</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Impairment expense (Notes 5 and 6)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>16.057567</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>1.918088</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>20.580912</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>OTHER INCOME (EXPENSE)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Gain on disposal of subsidiary (Note 11)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>0.54636</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>OTHER INCOME (EXPENSE)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Loss on investments (Notes 6 and 7)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>-0.348633</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>OTHER INCOME (EXPENSE)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>NET LOSS</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>-1.918088</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>-20.13164</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>OTHER COMPREHENSIVE INCOME</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Translation surplus</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>0.115162</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>OTHER COMPREHENSIVE INCOME</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>COMPREHENSIVE LOSS $</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>-1.918088</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>-20.016478</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>OTHER COMPREHENSIVE INCOME</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>-2.5e-07</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>-3.4e-07</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>OTHER COMPREHENSIVE INCOME</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>7.796974</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>58.997039</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>31, 2025          Ended January</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>(Restated Note 15) 31,</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Consulting fees $ 13,866 $</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>0.072121</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss 36,723</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>0.006582</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>General and administrative costs (Note 10) 183,096</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>0.258032</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Interest expense (Note 7) 10,078</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>0.005961</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Management fees (Note 10) 193,000</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Marketing fees 29,899</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>0.008392999999999999</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Professional fees 158,857</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="n">
+        <v>0.160431</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Stock-based compensation (Notes 9 and 10) 21,989</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="n">
+        <v>0.446865</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Transfer agent, regulatory and listing fees 25,954</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="n">
+        <v>0.021742</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Impairment of mineral properties (Note 5) 944,626</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="n">
+        <v>3.034927</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Loss on settlement of debt (Notes 7, 8 and 15) 300,000</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>LOSS AND COMPREHENSIVE LOSS $ (1,918,088) $</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="n">
+        <v>-4.213054</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share (Note 15) $ (0.25) $</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>-7.4e-07</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
         <is>
           <t>Weighted average number of common shares</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>Weighted average number of common shares outstanding 7,796,974</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D157" t="inlineStr">
         <is>
           <t>SharesOutstanding</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F85" s="5" t="n">
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="n">
         <v>5.669713</v>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G157" t="inlineStr">
         <is>
           <t>-</t>
         </is>
